--- a/BA/Part 1_Stakeholder Analysis amp Management-20260912/Done/AI/Artifacts/3. RACI Matrix_VNS.xlsx
+++ b/BA/Part 1_Stakeholder Analysis amp Management-20260912/Done/AI/Artifacts/3. RACI Matrix_VNS.xlsx
@@ -129,17 +129,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E7E6E6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00C6E0B4"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFE699"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E7E6E6"/>
       </patternFill>
     </fill>
   </fills>
@@ -251,16 +251,16 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -634,22 +634,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:P43"/>
+  <dimension ref="B2:P44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="72" customWidth="1" min="2" max="2"/>
-    <col width="6.6" customWidth="1" min="3" max="3"/>
-    <col width="6.6" customWidth="1" min="4" max="4"/>
-    <col width="6.6" customWidth="1" min="5" max="5"/>
-    <col width="6.6" customWidth="1" min="6" max="6"/>
-    <col width="6.6" customWidth="1" min="7" max="7"/>
-    <col width="6.6" customWidth="1" min="8" max="8"/>
-    <col width="6.6" customWidth="1" min="9" max="9"/>
-    <col width="6.6" customWidth="1" min="10" max="10"/>
-    <col width="6.6" customWidth="1" min="11" max="11"/>
-    <col width="6.6" customWidth="1" min="12" max="12"/>
-    <col width="6.6" customWidth="1" min="13" max="13"/>
+    <col width="6.8" customWidth="1" min="3" max="3"/>
+    <col width="6.8" customWidth="1" min="4" max="4"/>
+    <col width="6.8" customWidth="1" min="5" max="5"/>
+    <col width="6.8" customWidth="1" min="6" max="6"/>
+    <col width="6.8" customWidth="1" min="7" max="7"/>
+    <col width="6.8" customWidth="1" min="8" max="8"/>
+    <col width="6.8" customWidth="1" min="9" max="9"/>
+    <col width="6.8" customWidth="1" min="10" max="10"/>
+    <col width="6.8" customWidth="1" min="11" max="11"/>
+    <col width="6.8" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="2" ht="26" customHeight="1">
@@ -678,7 +677,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>V1.1</t>
+          <t>V1.2</t>
         </is>
       </c>
       <c r="H4" s="4" t="n"/>
@@ -689,7 +688,7 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="L4" s="4" t="n"/>
@@ -741,7 +740,7 @@
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>Nataliia Shakhovska (Executive Sponsor, Rector)</t>
+          <t>Ministry of Education and Science (Sponsor, regulator)</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
@@ -761,32 +760,27 @@
       </c>
       <c r="H7" s="11" t="inlineStr">
         <is>
-          <t>Tech Lead (D. Lunhul)</t>
+          <t>Tech Lead / SWE (D. Lunhul)</t>
         </is>
       </c>
       <c r="I7" s="11" t="inlineStr">
         <is>
-          <t>DevOps (Y. Shevchuk)</t>
+          <t>DevOps / SWE (Y. Shevchuk)</t>
         </is>
       </c>
       <c r="J7" s="11" t="inlineStr">
         <is>
-          <t>QA Specialist (V. Kamelchuk)</t>
+          <t>QA / SWE (V. Kamelchuk)</t>
         </is>
       </c>
       <c r="K7" s="11" t="inlineStr">
         <is>
-          <t>Nataliia Boiko (Customer / End user)</t>
+          <t>Technical Department of Lviv Polytechnic</t>
         </is>
       </c>
       <c r="L7" s="11" t="inlineStr">
         <is>
-          <t>Technical Department of Lviv Polytechnic</t>
-        </is>
-      </c>
-      <c r="M7" s="11" t="inlineStr">
-        <is>
-          <t>End users — students</t>
+          <t>End users — students and lecturers</t>
         </is>
       </c>
     </row>
@@ -808,52 +802,43 @@
           <t>A</t>
         </is>
       </c>
-      <c r="D9" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="E9" s="15" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="F9" s="15" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="G9" s="15" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="H9" s="16" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="I9" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="J9" s="14" t="inlineStr">
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="14" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F9" s="14" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="G9" s="14" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H9" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I9" s="16" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="J9" s="16" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
       <c r="K9" s="16" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="L9" s="16" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="M9" s="16" t="inlineStr">
+          <t>I</t>
+        </is>
+      </c>
+      <c r="L9" s="15" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -865,17 +850,13 @@
           <t xml:space="preserve"> - Identify and analyse stakeholders (register, power/interest matrix)</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D10" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="E10" s="16" t="inlineStr">
+      <c r="C10" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="15" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -885,37 +866,28 @@
           <t>A</t>
         </is>
       </c>
-      <c r="G10" s="15" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="H10" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="I10" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="J10" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="K10" s="16" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="L10" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="M10" s="14" t="inlineStr">
+      <c r="G10" s="14" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H10" s="16" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="I10" s="16" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="J10" s="16" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="n"/>
+      <c r="L10" s="16" t="inlineStr">
         <is>
           <t>I</t>
         </is>
@@ -932,52 +904,43 @@
           <t>A</t>
         </is>
       </c>
-      <c r="D11" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="E11" s="15" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="F11" s="16" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G11" s="16" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H11" s="15" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="I11" s="16" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J11" s="14" t="inlineStr">
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="14" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F11" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G11" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H11" s="14" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="I11" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J11" s="16" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
       <c r="K11" s="16" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>I</t>
         </is>
       </c>
       <c r="L11" s="16" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="M11" s="14" t="inlineStr">
         <is>
           <t>I</t>
         </is>
@@ -989,14 +952,14 @@
           <t xml:space="preserve"> - Develop the business case and the success metrics</t>
         </is>
       </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D12" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
+      <c r="C12" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D12" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="E12" s="13" t="inlineStr">
@@ -1004,42 +967,33 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F12" s="15" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="G12" s="15" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="H12" s="16" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="I12" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="J12" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="K12" s="16" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="L12" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="M12" s="14" t="inlineStr">
+      <c r="F12" s="14" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="G12" s="14" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H12" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I12" s="16" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="J12" s="16" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="n"/>
+      <c r="L12" s="16" t="inlineStr">
         <is>
           <t>I</t>
         </is>
@@ -1051,57 +1005,48 @@
           <t xml:space="preserve"> - Approve the project charter and the MVP scope</t>
         </is>
       </c>
-      <c r="C13" s="16" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D13" s="13" t="inlineStr">
+      <c r="C13" s="13" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="E13" s="15" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="F13" s="15" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="G13" s="16" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H13" s="16" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="I13" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="J13" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="K13" s="16" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="L13" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="M13" s="14" t="inlineStr">
+      <c r="D13" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E13" s="14" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F13" s="14" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="G13" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H13" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I13" s="16" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="J13" s="16" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="n"/>
+      <c r="L13" s="16" t="inlineStr">
         <is>
           <t>I</t>
         </is>
@@ -1117,23 +1062,23 @@
     <row r="15" ht="30" customHeight="1">
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> - Elicit and document requirements (customer interviews, end-user surveys)</t>
-        </is>
-      </c>
-      <c r="C15" s="14" t="inlineStr">
+          <t xml:space="preserve"> - Elicit and document requirements (interviews with lecturers, student surveys)</t>
+        </is>
+      </c>
+      <c r="C15" s="16" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
       <c r="D15" s="5" t="n"/>
-      <c r="E15" s="16" t="inlineStr">
+      <c r="E15" s="15" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
       <c r="F15" s="16" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>I</t>
         </is>
       </c>
       <c r="G15" s="13" t="inlineStr">
@@ -1141,32 +1086,23 @@
           <t>R/A</t>
         </is>
       </c>
-      <c r="H15" s="16" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="I15" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="J15" s="16" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K15" s="16" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="L15" s="16" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="M15" s="16" t="inlineStr">
+      <c r="H15" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I15" s="16" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="J15" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="n"/>
+      <c r="L15" s="15" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -1178,20 +1114,16 @@
           <t xml:space="preserve"> - Build UML models (use case, activity) for the product scenarios</t>
         </is>
       </c>
-      <c r="C16" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
+      <c r="C16" s="5" t="n"/>
       <c r="D16" s="5" t="n"/>
-      <c r="E16" s="16" t="inlineStr">
+      <c r="E16" s="15" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
       <c r="F16" s="16" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>I</t>
         </is>
       </c>
       <c r="G16" s="13" t="inlineStr">
@@ -1199,32 +1131,23 @@
           <t>R/A</t>
         </is>
       </c>
-      <c r="H16" s="16" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="I16" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="J16" s="16" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K16" s="16" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="L16" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="M16" s="14" t="inlineStr">
+      <c r="H16" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I16" s="16" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="J16" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="n"/>
+      <c r="L16" s="16" t="inlineStr">
         <is>
           <t>I</t>
         </is>
@@ -1236,23 +1159,19 @@
           <t xml:space="preserve"> - Design the data model and the custom backend architecture</t>
         </is>
       </c>
-      <c r="C17" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
+      <c r="C17" s="5" t="n"/>
       <c r="D17" s="5" t="n"/>
-      <c r="E17" s="16" t="inlineStr">
+      <c r="E17" s="15" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
       <c r="F17" s="16" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G17" s="16" t="inlineStr">
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G17" s="15" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -1262,27 +1181,18 @@
           <t>R/A</t>
         </is>
       </c>
-      <c r="I17" s="15" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="J17" s="16" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K17" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="L17" s="16" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="M17" s="5" t="n"/>
+      <c r="I17" s="14" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="J17" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="n"/>
+      <c r="L17" s="5" t="n"/>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="B18" s="3" t="inlineStr">
@@ -1295,52 +1205,47 @@
           <t>A</t>
         </is>
       </c>
-      <c r="D18" s="16" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E18" s="16" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F18" s="15" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="G18" s="15" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="H18" s="16" t="inlineStr">
+      <c r="D18" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E18" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F18" s="14" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="G18" s="14" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H18" s="15" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
       <c r="I18" s="16" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J18" s="14" t="inlineStr">
+          <t>I</t>
+        </is>
+      </c>
+      <c r="J18" s="16" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
       <c r="K18" s="16" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>I</t>
         </is>
       </c>
       <c r="L18" s="16" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="M18" s="14" t="inlineStr">
         <is>
           <t>I</t>
         </is>
@@ -1352,17 +1257,13 @@
           <t xml:space="preserve"> - Produce the communications plan and the project schedule</t>
         </is>
       </c>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D19" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="E19" s="16" t="inlineStr">
+      <c r="C19" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="n"/>
+      <c r="E19" s="15" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -1372,41 +1273,28 @@
           <t>R/A</t>
         </is>
       </c>
-      <c r="G19" s="15" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="H19" s="16" t="inlineStr">
+      <c r="G19" s="14" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H19" s="15" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
       <c r="I19" s="16" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>I</t>
         </is>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K19" s="16" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="L19" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="M19" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="n"/>
+      <c r="L19" s="5" t="n"/>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="B20" s="3" t="inlineStr">
@@ -1414,29 +1302,25 @@
           <t xml:space="preserve"> - Select the technology stack and the LLM API provider</t>
         </is>
       </c>
-      <c r="C20" s="16" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D20" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="E20" s="16" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F20" s="16" t="inlineStr">
+      <c r="C20" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F20" s="15" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
       <c r="G20" s="16" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>I</t>
         </is>
       </c>
       <c r="H20" s="13" t="inlineStr">
@@ -1444,27 +1328,18 @@
           <t>A</t>
         </is>
       </c>
-      <c r="I20" s="15" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="J20" s="16" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K20" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="L20" s="16" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="M20" s="5" t="n"/>
+      <c r="I20" s="14" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="J20" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="n"/>
+      <c r="L20" s="5" t="n"/>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="B21" s="12" t="inlineStr">
@@ -1479,53 +1354,48 @@
           <t xml:space="preserve"> - Obtain the student registry; implement registration and authentication</t>
         </is>
       </c>
-      <c r="C22" s="16" t="inlineStr">
+      <c r="C22" s="15" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
       <c r="D22" s="5" t="n"/>
-      <c r="E22" s="16" t="inlineStr">
+      <c r="E22" s="15" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
       <c r="F22" s="16" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G22" s="16" t="inlineStr">
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G22" s="15" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
       <c r="H22" s="13" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="I22" s="15" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="J22" s="16" t="inlineStr">
-        <is>
-          <t>C</t>
+          <t>R/A</t>
+        </is>
+      </c>
+      <c r="I22" s="14" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="J22" s="14" t="inlineStr">
+        <is>
+          <t>R</t>
         </is>
       </c>
       <c r="K22" s="14" t="inlineStr">
         <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="L22" s="15" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="M22" s="14" t="inlineStr">
+          <t>R</t>
+        </is>
+      </c>
+      <c r="L22" s="16" t="inlineStr">
         <is>
           <t>I</t>
         </is>
@@ -1537,23 +1407,19 @@
           <t xml:space="preserve"> - Implement courses, materials, deadlines and grade forecasting</t>
         </is>
       </c>
-      <c r="C23" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
+      <c r="C23" s="5" t="n"/>
       <c r="D23" s="5" t="n"/>
-      <c r="E23" s="16" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F23" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="G23" s="16" t="inlineStr">
+      <c r="E23" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F23" s="16" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G23" s="15" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -1565,27 +1431,18 @@
       </c>
       <c r="I23" s="14" t="inlineStr">
         <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="J23" s="16" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K23" s="16" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="L23" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="M23" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="J23" s="14" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="n"/>
+      <c r="L23" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -1595,23 +1452,19 @@
           <t xml:space="preserve"> - Implement the communication hub and Study Spaces</t>
         </is>
       </c>
-      <c r="C24" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
+      <c r="C24" s="5" t="n"/>
       <c r="D24" s="5" t="n"/>
-      <c r="E24" s="16" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F24" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="G24" s="16" t="inlineStr">
+      <c r="E24" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F24" s="16" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G24" s="15" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -1621,27 +1474,18 @@
           <t>R/A</t>
         </is>
       </c>
-      <c r="I24" s="15" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="J24" s="16" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K24" s="16" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="L24" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="M24" s="16" t="inlineStr">
+      <c r="I24" s="14" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="J24" s="14" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="n"/>
+      <c r="L24" s="15" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -1653,7 +1497,7 @@
           <t xml:space="preserve"> - Implement the AI assistant: summaries, quizzes, “Ask the course”</t>
         </is>
       </c>
-      <c r="C25" s="14" t="inlineStr">
+      <c r="C25" s="16" t="inlineStr">
         <is>
           <t>I</t>
         </is>
@@ -1664,42 +1508,33 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F25" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="G25" s="16" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H25" s="15" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="I25" s="15" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="J25" s="16" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K25" s="16" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="L25" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="M25" s="16" t="inlineStr">
+      <c r="F25" s="16" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G25" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H25" s="14" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="I25" s="14" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="J25" s="14" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="n"/>
+      <c r="L25" s="15" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -1711,49 +1546,40 @@
           <t xml:space="preserve"> - Set up environments and configure CI/CD</t>
         </is>
       </c>
-      <c r="C26" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
+      <c r="C26" s="5" t="n"/>
       <c r="D26" s="5" t="n"/>
-      <c r="E26" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="F26" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="G26" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="H26" s="16" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="I26" s="13" t="inlineStr">
-        <is>
-          <t>R/A</t>
-        </is>
-      </c>
-      <c r="J26" s="16" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K26" s="5" t="n"/>
-      <c r="L26" s="16" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="M26" s="5" t="n"/>
+      <c r="E26" s="16" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F26" s="16" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="n"/>
+      <c r="H26" s="13" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I26" s="14" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="J26" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K26" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L26" s="5" t="n"/>
     </row>
     <row r="27" ht="30" customHeight="1">
       <c r="B27" s="3" t="inlineStr">
@@ -1761,252 +1587,212 @@
           <t xml:space="preserve"> - Run testing and acceptance checks</t>
         </is>
       </c>
-      <c r="C27" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
+      <c r="C27" s="5" t="n"/>
       <c r="D27" s="5" t="n"/>
-      <c r="E27" s="16" t="inlineStr">
-        <is>
-          <t>C</t>
+      <c r="E27" s="13" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="F27" s="16" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G27" s="16" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H27" s="16" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="I27" s="16" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J27" s="13" t="inlineStr">
-        <is>
-          <t>R/A</t>
-        </is>
-      </c>
-      <c r="K27" s="16" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="L27" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="M27" s="16" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="20" customHeight="1">
-      <c r="B28" s="12" t="inlineStr">
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G27" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H27" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I27" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J27" s="14" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="n"/>
+      <c r="L27" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - Deploy the platform to the production environment</t>
+        </is>
+      </c>
+      <c r="C28" s="16" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="n"/>
+      <c r="E28" s="16" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F28" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G28" s="16" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="H28" s="13" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I28" s="14" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="J28" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K28" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L28" s="16" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="B29" s="12" t="inlineStr">
         <is>
           <t>Control Phase</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="30" customHeight="1">
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> - Manage scope changes and backlog priorities</t>
-        </is>
-      </c>
-      <c r="C29" s="16" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D29" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="E29" s="13" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F29" s="15" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="G29" s="15" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="H29" s="16" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="I29" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="J29" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="K29" s="16" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="L29" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="M29" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
         </is>
       </c>
     </row>
     <row r="30" ht="30" customHeight="1">
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> - Control quality, defects and adherence to the acceptance criteria</t>
-        </is>
-      </c>
-      <c r="C30" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
+          <t xml:space="preserve"> - Manage scope changes and backlog priorities</t>
+        </is>
+      </c>
+      <c r="C30" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="D30" s="5" t="n"/>
-      <c r="E30" s="16" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F30" s="16" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G30" s="16" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H30" s="16" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="I30" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="J30" s="13" t="inlineStr">
-        <is>
-          <t>R/A</t>
-        </is>
-      </c>
-      <c r="K30" s="16" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="L30" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="M30" s="16" t="inlineStr">
-        <is>
-          <t>C</t>
+      <c r="E30" s="13" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F30" s="14" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="G30" s="14" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H30" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I30" s="16" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="J30" s="16" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="n"/>
+      <c r="L30" s="16" t="inlineStr">
+        <is>
+          <t>I</t>
         </is>
       </c>
     </row>
     <row r="31" ht="30" customHeight="1">
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> - Monitor LLM API costs, quotas and request limits</t>
-        </is>
-      </c>
-      <c r="C31" s="16" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D31" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="E31" s="16" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F31" s="13" t="inlineStr">
-        <is>
-          <t>R/A</t>
-        </is>
-      </c>
-      <c r="G31" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="H31" s="16" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="I31" s="15" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="J31" s="5" t="n"/>
+          <t xml:space="preserve"> - Control quality, defects and adherence to the acceptance criteria</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="n"/>
+      <c r="D31" s="5" t="n"/>
+      <c r="E31" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F31" s="16" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G31" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H31" s="13" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I31" s="16" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="J31" s="14" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="K31" s="5" t="n"/>
-      <c r="L31" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="M31" s="5" t="n"/>
+      <c r="L31" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="30" customHeight="1">
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> - Report project status to the sponsors and the Rector's office</t>
-        </is>
-      </c>
-      <c r="C32" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="D32" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="E32" s="16" t="inlineStr">
+          <t xml:space="preserve"> - Monitor LLM API costs, quotas and request limits</t>
+        </is>
+      </c>
+      <c r="C32" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="n"/>
+      <c r="E32" s="15" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -2016,324 +1802,301 @@
           <t>R/A</t>
         </is>
       </c>
-      <c r="G32" s="15" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="H32" s="16" t="inlineStr">
+      <c r="G32" s="5" t="n"/>
+      <c r="H32" s="15" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
       <c r="I32" s="14" t="inlineStr">
         <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="J32" s="16" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K32" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="L32" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="M32" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="20" customHeight="1">
-      <c r="B33" s="12" t="inlineStr">
+          <t>R</t>
+        </is>
+      </c>
+      <c r="J32" s="5" t="n"/>
+      <c r="K32" s="5" t="n"/>
+      <c r="L32" s="5" t="n"/>
+    </row>
+    <row r="33" ht="30" customHeight="1">
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - Report project status to the sponsors</t>
+        </is>
+      </c>
+      <c r="C33" s="16" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D33" s="16" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E33" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F33" s="13" t="inlineStr">
+        <is>
+          <t>R/A</t>
+        </is>
+      </c>
+      <c r="G33" s="14" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H33" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="n"/>
+      <c r="J33" s="5" t="n"/>
+      <c r="K33" s="5" t="n"/>
+      <c r="L33" s="5" t="n"/>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="B34" s="12" t="inlineStr">
         <is>
           <t>Close Phase</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="30" customHeight="1">
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> - Run the pilot with students and collect feedback</t>
-        </is>
-      </c>
-      <c r="C34" s="16" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D34" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="E34" s="13" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F34" s="15" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="G34" s="15" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="H34" s="16" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="I34" s="16" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J34" s="16" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K34" s="15" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="L34" s="16" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="M34" s="15" t="inlineStr">
-        <is>
-          <t>R</t>
         </is>
       </c>
     </row>
     <row r="35" ht="30" customHeight="1">
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> - Hand over the system and documentation to the Technical Department and the customer</t>
-        </is>
-      </c>
-      <c r="C35" s="16" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D35" s="16" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E35" s="15" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="F35" s="13" t="inlineStr">
+          <t xml:space="preserve"> - Run the pilot with students and lecturers and collect feedback</t>
+        </is>
+      </c>
+      <c r="C35" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="n"/>
+      <c r="E35" s="13" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="G35" s="15" t="inlineStr">
+      <c r="F35" s="14" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="G35" s="14" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
       <c r="H35" s="15" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I35" s="15" t="inlineStr">
         <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="J35" s="16" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K35" s="16" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="L35" s="15" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="M35" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J35" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="n"/>
+      <c r="L35" s="14" t="inlineStr">
+        <is>
+          <t>R</t>
         </is>
       </c>
     </row>
     <row r="36" ht="30" customHeight="1">
       <c r="B36" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve"> - Hand over the system and documentation to the sponsor</t>
+        </is>
+      </c>
+      <c r="C36" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="n"/>
+      <c r="E36" s="14" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F36" s="13" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G36" s="14" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H36" s="14" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="I36" s="14" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="J36" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K36" s="16" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="L36" s="5" t="n"/>
+    </row>
+    <row r="37" ht="30" customHeight="1">
+      <c r="B37" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve"> - Capture lessons learned and close the project</t>
         </is>
       </c>
-      <c r="C36" s="16" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D36" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="E36" s="16" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F36" s="13" t="inlineStr">
+      <c r="C37" s="16" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="n"/>
+      <c r="E37" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F37" s="13" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="G36" s="15" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="H36" s="16" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="I36" s="16" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J36" s="16" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K36" s="16" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="L36" s="16" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="M36" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="17" t="inlineStr">
+      <c r="G37" s="14" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H37" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I37" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J37" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="n"/>
+      <c r="L37" s="5" t="n"/>
+    </row>
+    <row r="39">
+      <c r="B39" s="17" t="inlineStr">
         <is>
           <t>LEGEND</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="26" customHeight="1">
-      <c r="B39" s="18" t="inlineStr">
+    <row r="40" ht="30" customHeight="1">
+      <c r="B40" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">  R  —  Responsible</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr">
+      <c r="C40" s="3" t="inlineStr">
         <is>
           <t>People or stakeholders who do the work. Several roles can be jointly Responsible.</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="26" customHeight="1">
-      <c r="B40" s="19" t="inlineStr">
+    <row r="41" ht="30" customHeight="1">
+      <c r="B41" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">  A  —  Accountable</t>
         </is>
       </c>
-      <c r="C40" s="3" t="inlineStr">
-        <is>
-          <t>The owner of the work, who signs off or approves it when complete. Exactly one role is Accountable for each activity.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="26" customHeight="1">
-      <c r="B41" s="20" t="inlineStr">
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>The owner of the work, who signs off or approves it when complete. Exactly one role is Accountable for each activity, and only roles with high influence are ever Accountable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="30" customHeight="1">
+      <c r="B42" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">  C  —  Consulted</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr">
+      <c r="C42" s="3" t="inlineStr">
         <is>
           <t>People whose input is needed before the work can be done and signed off. Two-way communication.</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="26" customHeight="1">
-      <c r="B42" s="21" t="inlineStr">
+    <row r="43" ht="30" customHeight="1">
+      <c r="B43" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">  I  —  Informed</t>
         </is>
       </c>
-      <c r="C42" s="3" t="inlineStr">
+      <c r="C43" s="3" t="inlineStr">
         <is>
           <t>People who need to be kept in the picture. One-way communication, no direct contribution.</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="26" customHeight="1">
-      <c r="B43" s="19" t="inlineStr">
+    <row r="44" ht="30" customHeight="1">
+      <c r="B44" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">  R/A  —  Combination</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr">
-        <is>
-          <t>The role both does the work and owns the result — typical for the BA on requirements, QA on testing and DevOps on environments.</t>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>The role both does the work and owns the result — typical for the BA on requirements and the Tech Lead on architecture and implementation.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="B2:M2"/>
     <mergeCell ref="I6:J6"/>
-    <mergeCell ref="B8:M8"/>
-    <mergeCell ref="B14:M14"/>
-    <mergeCell ref="C42:M42"/>
+    <mergeCell ref="K4:L4"/>
     <mergeCell ref="C4:D4"/>
-    <mergeCell ref="B38:M38"/>
-    <mergeCell ref="B28:M28"/>
-    <mergeCell ref="C41:M41"/>
+    <mergeCell ref="B21:L21"/>
+    <mergeCell ref="B39:L39"/>
+    <mergeCell ref="B2:L2"/>
+    <mergeCell ref="B14:L14"/>
+    <mergeCell ref="C42:L42"/>
     <mergeCell ref="O4:P4"/>
-    <mergeCell ref="C40:M40"/>
-    <mergeCell ref="B33:M33"/>
-    <mergeCell ref="C43:M43"/>
-    <mergeCell ref="K6:M6"/>
+    <mergeCell ref="B8:L8"/>
+    <mergeCell ref="B29:L29"/>
+    <mergeCell ref="B34:L34"/>
     <mergeCell ref="C6:E6"/>
+    <mergeCell ref="C44:L44"/>
+    <mergeCell ref="C41:L41"/>
     <mergeCell ref="G4:H4"/>
-    <mergeCell ref="C39:M39"/>
     <mergeCell ref="F6:H6"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="B21:M21"/>
+    <mergeCell ref="C40:L40"/>
+    <mergeCell ref="C43:L43"/>
+    <mergeCell ref="K6:L6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>
@@ -2346,7 +2109,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B25"/>
+  <dimension ref="B2:B27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -2446,49 +2209,63 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="8" customHeight="1">
-      <c r="B18" s="22" t="inlineStr"/>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="B19" s="23" t="inlineStr">
+    <row r="18" ht="30" customHeight="1">
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  5. Only roles with high influence in the Stakeholder Register are ever Accountable. Low-influence roles (DevOps, QA, the Technical Department, end users) can be Responsible or Consulted, but never sign off.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  6. Tech Lead, DevOps and QA are all software engineers (SWE), so all three are Responsible for implementing the product modules.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="8" customHeight="1">
+      <c r="B20" s="22" t="inlineStr"/>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="B21" s="23" t="inlineStr">
         <is>
           <t>Relationship to the other artifacts:</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="B20" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - The roles in the columns correspond to the entries in “1. Stakeholder Register_VNS.xlsx”.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="B21" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - Stakeholders marked Key Player in the register hold A or R in the key phases of this matrix.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="B22" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - Stakeholders marked Keep Informed mostly hold I and C.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="30" customHeight="1">
+          <t xml:space="preserve">  - The roles in the columns correspond to the entries in “1. Stakeholder Register_VNS.xlsx”.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1">
       <c r="B23" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - The frequency and format of interaction for roles holding A, R or C are detailed in “4. Communication Plan_VNS.xlsx”.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="8" customHeight="1">
-      <c r="B24" s="22" t="inlineStr"/>
+          <t xml:space="preserve">  - Stakeholders marked Key Player in the register hold A or R in the key phases of this matrix.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="B24" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Stakeholders with low interest (the Ministry, the Project Manager, the Technical Department) are consulted only on decisions that concern them and are otherwise informed or not involved.</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="B25" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - The frequency and format of interaction for roles holding A, R or C are detailed in “4. Communication Plan_VNS.xlsx”.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="8" customHeight="1">
+      <c r="B26" s="22" t="inlineStr"/>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="B27" s="22" t="inlineStr">
         <is>
           <t>Demonstration note: this is a training business case. The university stakeholders named here are addressed in a demonstration context and no real agreements have been concluded with them.</t>
         </is>
